--- a/01_用AI生成Excel/11_圖表/月營收圖表.xlsx
+++ b/01_用AI生成Excel/11_圖表/月營收圖表.xlsx
@@ -73,7 +73,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -81,6 +81,7 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -306,30 +307,6 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'季彙總'!B1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'季彙總'!$A$2:$A$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'季彙總'!$B$2:$B$5</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
               <f>'季彙總'!C1</f>
             </strRef>
           </tx>
@@ -346,6 +323,30 @@
           <val>
             <numRef>
               <f>'季彙總'!$C$2:$C$5</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'季彙總'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'季彙總'!$A$2:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'季彙總'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -548,6 +549,21 @@
     <clientData/>
   </oneCellAnchor>
 </wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_Revenue" displayName="T_Revenue" ref="A1:D13" headerRowCount="1">
+  <autoFilter ref="A1:D13"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="月份"/>
+    <tableColumn id="2" name="門市營收"/>
+    <tableColumn id="3" name="線上營收"/>
+    <tableColumn id="4" name="合計營收">
+      <calculatedColumnFormula>T_Revenue[[#This Row],[門市營收]]+T_Revenue[[#This Row],[線上營收]]</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -881,7 +897,7 @@
         <v>310000</v>
       </c>
       <c r="D2" s="3">
-        <f>B2+C2</f>
+        <f>T_Revenue[[#This Row],[門市營收]]+T_Revenue[[#This Row],[線上營收]]</f>
         <v/>
       </c>
     </row>
@@ -896,7 +912,7 @@
         <v>290000</v>
       </c>
       <c r="D3" s="3">
-        <f>B3+C3</f>
+        <f>T_Revenue[[#This Row],[門市營收]]+T_Revenue[[#This Row],[線上營收]]</f>
         <v/>
       </c>
     </row>
@@ -911,7 +927,7 @@
         <v>350000</v>
       </c>
       <c r="D4" s="3">
-        <f>B4+C4</f>
+        <f>T_Revenue[[#This Row],[門市營收]]+T_Revenue[[#This Row],[線上營收]]</f>
         <v/>
       </c>
     </row>
@@ -926,7 +942,7 @@
         <v>380000</v>
       </c>
       <c r="D5" s="3">
-        <f>B5+C5</f>
+        <f>T_Revenue[[#This Row],[門市營收]]+T_Revenue[[#This Row],[線上營收]]</f>
         <v/>
       </c>
     </row>
@@ -941,7 +957,7 @@
         <v>420000</v>
       </c>
       <c r="D6" s="3">
-        <f>B6+C6</f>
+        <f>T_Revenue[[#This Row],[門市營收]]+T_Revenue[[#This Row],[線上營收]]</f>
         <v/>
       </c>
     </row>
@@ -956,7 +972,7 @@
         <v>460000</v>
       </c>
       <c r="D7" s="3">
-        <f>B7+C7</f>
+        <f>T_Revenue[[#This Row],[門市營收]]+T_Revenue[[#This Row],[線上營收]]</f>
         <v/>
       </c>
     </row>
@@ -971,7 +987,7 @@
         <v>500000</v>
       </c>
       <c r="D8" s="3">
-        <f>B8+C8</f>
+        <f>T_Revenue[[#This Row],[門市營收]]+T_Revenue[[#This Row],[線上營收]]</f>
         <v/>
       </c>
     </row>
@@ -986,7 +1002,7 @@
         <v>530000</v>
       </c>
       <c r="D9" s="3">
-        <f>B9+C9</f>
+        <f>T_Revenue[[#This Row],[門市營收]]+T_Revenue[[#This Row],[線上營收]]</f>
         <v/>
       </c>
     </row>
@@ -1001,7 +1017,7 @@
         <v>560000</v>
       </c>
       <c r="D10" s="3">
-        <f>B10+C10</f>
+        <f>T_Revenue[[#This Row],[門市營收]]+T_Revenue[[#This Row],[線上營收]]</f>
         <v/>
       </c>
     </row>
@@ -1016,7 +1032,7 @@
         <v>600000</v>
       </c>
       <c r="D11" s="3">
-        <f>B11+C11</f>
+        <f>T_Revenue[[#This Row],[門市營收]]+T_Revenue[[#This Row],[線上營收]]</f>
         <v/>
       </c>
     </row>
@@ -1031,7 +1047,7 @@
         <v>720000</v>
       </c>
       <c r="D12" s="3">
-        <f>B12+C12</f>
+        <f>T_Revenue[[#This Row],[門市營收]]+T_Revenue[[#This Row],[線上營收]]</f>
         <v/>
       </c>
     </row>
@@ -1046,12 +1062,15 @@
         <v>810000</v>
       </c>
       <c r="D13" s="3">
-        <f>B13+C13</f>
+        <f>T_Revenue[[#This Row],[門市營收]]+T_Revenue[[#This Row],[線上營收]]</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -1061,13 +1080,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1078,15 +1098,20 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>起始月份</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>門市營收</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>線上營收</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>合計營收</t>
         </is>
@@ -1098,16 +1123,19 @@
           <t>Q1</t>
         </is>
       </c>
-      <c r="B2" s="5">
-        <f>SUM('月營收'!B2:B4)</f>
-        <v/>
-      </c>
-      <c r="C2" s="5">
-        <f>SUM('月營收'!C2:C4)</f>
-        <v/>
-      </c>
-      <c r="D2" s="5">
-        <f>B2+C2</f>
+      <c r="B2" s="5" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C2" s="6">
+        <f>SUMIFS(T_Revenue[門市營收],T_Revenue[月份],"&gt;="&amp;$B2,T_Revenue[月份],"&lt;"&amp;EDATE($B2,3))</f>
+        <v/>
+      </c>
+      <c r="D2" s="6">
+        <f>SUMIFS(T_Revenue[線上營收],T_Revenue[月份],"&gt;="&amp;$B2,T_Revenue[月份],"&lt;"&amp;EDATE($B2,3))</f>
+        <v/>
+      </c>
+      <c r="E2" s="6">
+        <f>C2+D2</f>
         <v/>
       </c>
     </row>
@@ -1117,16 +1145,19 @@
           <t>Q2</t>
         </is>
       </c>
-      <c r="B3" s="5">
-        <f>SUM('月營收'!B5:B7)</f>
-        <v/>
-      </c>
-      <c r="C3" s="5">
-        <f>SUM('月營收'!C5:C7)</f>
-        <v/>
-      </c>
-      <c r="D3" s="5">
-        <f>B3+C3</f>
+      <c r="B3" s="5" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C3" s="6">
+        <f>SUMIFS(T_Revenue[門市營收],T_Revenue[月份],"&gt;="&amp;$B3,T_Revenue[月份],"&lt;"&amp;EDATE($B3,3))</f>
+        <v/>
+      </c>
+      <c r="D3" s="6">
+        <f>SUMIFS(T_Revenue[線上營收],T_Revenue[月份],"&gt;="&amp;$B3,T_Revenue[月份],"&lt;"&amp;EDATE($B3,3))</f>
+        <v/>
+      </c>
+      <c r="E3" s="6">
+        <f>C3+D3</f>
         <v/>
       </c>
     </row>
@@ -1136,16 +1167,19 @@
           <t>Q3</t>
         </is>
       </c>
-      <c r="B4" s="5">
-        <f>SUM('月營收'!B8:B10)</f>
-        <v/>
-      </c>
-      <c r="C4" s="5">
-        <f>SUM('月營收'!C8:C10)</f>
-        <v/>
-      </c>
-      <c r="D4" s="5">
-        <f>B4+C4</f>
+      <c r="B4" s="5" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C4" s="6">
+        <f>SUMIFS(T_Revenue[門市營收],T_Revenue[月份],"&gt;="&amp;$B4,T_Revenue[月份],"&lt;"&amp;EDATE($B4,3))</f>
+        <v/>
+      </c>
+      <c r="D4" s="6">
+        <f>SUMIFS(T_Revenue[線上營收],T_Revenue[月份],"&gt;="&amp;$B4,T_Revenue[月份],"&lt;"&amp;EDATE($B4,3))</f>
+        <v/>
+      </c>
+      <c r="E4" s="6">
+        <f>C4+D4</f>
         <v/>
       </c>
     </row>
@@ -1155,16 +1189,19 @@
           <t>Q4</t>
         </is>
       </c>
-      <c r="B5" s="5">
-        <f>SUM('月營收'!B11:B13)</f>
-        <v/>
-      </c>
-      <c r="C5" s="5">
-        <f>SUM('月營收'!C11:C13)</f>
-        <v/>
-      </c>
-      <c r="D5" s="5">
-        <f>B5+C5</f>
+      <c r="B5" s="5" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C5" s="6">
+        <f>SUMIFS(T_Revenue[門市營收],T_Revenue[月份],"&gt;="&amp;$B5,T_Revenue[月份],"&lt;"&amp;EDATE($B5,3))</f>
+        <v/>
+      </c>
+      <c r="D5" s="6">
+        <f>SUMIFS(T_Revenue[線上營收],T_Revenue[月份],"&gt;="&amp;$B5,T_Revenue[月份],"&lt;"&amp;EDATE($B5,3))</f>
+        <v/>
+      </c>
+      <c r="E5" s="6">
+        <f>C5+D5</f>
         <v/>
       </c>
     </row>
@@ -1186,8 +1223,8 @@
           <t>門市</t>
         </is>
       </c>
-      <c r="B9" s="5">
-        <f>SUM(B2:B5)</f>
+      <c r="B9" s="6">
+        <f>SUM(T_Revenue[門市營收])</f>
         <v/>
       </c>
     </row>
@@ -1197,8 +1234,8 @@
           <t>線上</t>
         </is>
       </c>
-      <c r="B10" s="5">
-        <f>SUM(C2:C5)</f>
+      <c r="B10" s="6">
+        <f>SUM(T_Revenue[線上營收])</f>
         <v/>
       </c>
     </row>
@@ -1217,7 +1254,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>三種問題，三種圖：趨勢 → 折線圖、比較 → 長條圖、組成 → 圓餅圖</t>
         </is>
